--- a/other/input/wqx_templates/wqx_template_matching_table.xlsx
+++ b/other/input/wqx_templates/wqx_template_matching_table.xlsx
@@ -276,8 +276,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -923,7 +922,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -1000,7 +999,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -1077,7 +1076,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -1172,7 +1171,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -1383,8 +1382,10 @@
       <c r="A19" t="n">
         <v>10000030</v>
       </c>
-      <c r="B19" t="s">
-        <v>21</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>KBL_m_50.0</t>
+        </is>
       </c>
       <c r="C19" t="s">
         <v>80</v>
@@ -1394,8 +1395,10 @@
       <c r="A20" t="n">
         <v>10000031</v>
       </c>
-      <c r="B20" t="s">
-        <v>22</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>KBL_m_70.0</t>
+        </is>
       </c>
       <c r="C20" t="s">
         <v>81</v>
@@ -1436,6 +1439,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>